--- a/data/processed/positivacao/2023-02_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2023-02_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -25387,7 +25387,7 @@
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B964" t="inlineStr"/>
@@ -36635,7 +36635,7 @@
     <row r="1397">
       <c r="A1397" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1397" t="inlineStr"/>
@@ -65579,7 +65579,7 @@
     <row r="2511">
       <c r="A2511" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2511" t="inlineStr"/>
@@ -67250,12 +67250,12 @@
       <c r="A2576" t="inlineStr"/>
       <c r="B2576" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 6 cliente(s), não positivou 89 cliente(s) - Total vendido: R$ 18.703,92
+          <t>Vendedor 1 - VENDEDOR 01: positivou 6 cliente(s), não positivou 89 cliente(s) - Total vendido: R$ 18.703,92
 Vendedor 18 - LOJA: positivou 134 cliente(s), não positivou 725 cliente(s) - Total vendido: R$ 61.079,86
-Vendedor 3 - FERNANDA: positivou 104 cliente(s), não positivou 328 cliente(s) - Total vendido: R$ 161.639,49
-Vendedor 4 - DANIELA: positivou 68 cliente(s), não positivou 593 cliente(s) - Total vendido: R$ 41.380,22
+Vendedor 3 - VENDEDOR 03: positivou 104 cliente(s), não positivou 328 cliente(s) - Total vendido: R$ 161.639,49
+Vendedor 4 - VENDEDOR 04: positivou 68 cliente(s), não positivou 593 cliente(s) - Total vendido: R$ 41.380,22
 Vendedor 5 - SITE: positivou 6 cliente(s), não positivou 445 cliente(s) - Total vendido: R$ 1.143,40
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2576" t="inlineStr"/>
